--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104507_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104507_W6.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.824</v>
+        <v>5.8428</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7</v>
+        <v>4.7472</v>
       </c>
       <c r="F2" t="n">
-        <v>2.124</v>
+        <v>1.0957</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6517</v>
+        <v>4.9658</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0043</v>
+        <v>0.6862</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6473</v>
+        <v>4.2796</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0938</v>
+        <v>5.5812</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2729</v>
+        <v>1.4479</v>
       </c>
       <c r="L2" t="n">
-        <v>0.821</v>
+        <v>4.1333</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5578</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2685</v>
+        <v>-0.7617</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8264</v>
+        <v>0.1463</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4218</v>
+        <v>1.1046</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0294</v>
+        <v>0.3042</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3924</v>
+        <v>0.8005</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.7032</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.2891</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4429</v>
+        <v>5.7051</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5576</v>
+        <v>5.6978</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1147</v>
+        <v>0.0073</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5693</v>
+        <v>1.5666</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0362</v>
+        <v>1.0286</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5331</v>
+        <v>0.538</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8723</v>
+        <v>1.8516</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1633</v>
+        <v>1.1441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.303</v>
+        <v>-0.2851</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0758</v>
+        <v>0.345</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0858</v>
+        <v>0.2622</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.01</v>
+        <v>0.0827</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5994</v>
+        <v>3.584</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5781</v>
+        <v>5.4841</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4112</v>
+        <v>4.0262</v>
       </c>
       <c r="F4" t="n">
-        <v>1.167</v>
+        <v>1.4578</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9633</v>
+        <v>2.9171</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6825</v>
+        <v>1.031</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2808</v>
+        <v>1.8862</v>
       </c>
       <c r="J4" t="n">
-        <v>5.5968</v>
+        <v>2.7139</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1422</v>
+        <v>1.2661</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6335</v>
+        <v>0.2032</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7721</v>
+        <v>-0.4169</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1387</v>
+        <v>0.6201</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8417</v>
+        <v>0.6156</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0514</v>
+        <v>0.2715</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8931</v>
+        <v>0.3441</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4037</v>
+        <v>5.163</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0921</v>
+        <v>3.4439</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3116</v>
+        <v>1.7191</v>
       </c>
       <c r="G5" t="n">
-        <v>2.908</v>
+        <v>4.6525</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0288</v>
+        <v>2.9988</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8793</v>
+        <v>1.6538</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7234</v>
+        <v>4.077</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4546</v>
+        <v>3.2578</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2688</v>
+        <v>0.8192</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1847</v>
+        <v>0.5755</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4258</v>
+        <v>-0.259</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6105</v>
+        <v>0.8345</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5371</v>
+        <v>1.7609</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3176</v>
+        <v>0.8057</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2196</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1853</v>
+        <v>-1.7057</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>-0.3007</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8956</v>
+        <v>4.2032</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5575</v>
+        <v>4.4808</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3381</v>
+        <v>-0.2776</v>
       </c>
       <c r="G6" t="n">
-        <v>1.445</v>
+        <v>2.0336</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4054</v>
+        <v>1.1027</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0396</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6553</v>
+        <v>3.7369</v>
       </c>
       <c r="K6" t="n">
-        <v>0.658</v>
+        <v>1.7786</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0027</v>
+        <v>1.9582</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7896</v>
+        <v>-1.7032</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2526</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0423</v>
+        <v>-1.0273</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4506</v>
+        <v>0.3485</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1905</v>
+        <v>0.0414</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6412</v>
+        <v>0.3071</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1817</v>
+        <v>4.1395</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4994</v>
+        <v>1.7831</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3177</v>
+        <v>2.3564</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0324</v>
+        <v>1.4518</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0995</v>
+        <v>0.4104</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9329</v>
+        <v>1.0413</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7662</v>
+        <v>0.6473</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7938</v>
+        <v>0.655</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9724</v>
+        <v>-0.0077</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7338</v>
+        <v>0.8044</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6944</v>
+        <v>-0.2446</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0395</v>
+        <v>1.049</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6654</v>
+        <v>0.6878</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9739</v>
+        <v>0.0463</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3085</v>
+        <v>0.6415</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.357</v>
+        <v>1.562</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1687</v>
+        <v>1.6981</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1883</v>
+        <v>-0.1361</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6589</v>
+        <v>0.6573</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4792</v>
+        <v>-0.4714</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1381</v>
+        <v>1.1287</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5165</v>
+        <v>1.5031</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8576</v>
+        <v>-0.8458</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6566</v>
+        <v>0.8561</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3478</v>
+        <v>0.195</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0044</v>
+        <v>0.6611</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2893</v>
+        <v>0.4401</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2984</v>
+        <v>-1.3633</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5876</v>
+        <v>1.8034</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0544</v>
+        <v>-2.0514</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3982</v>
+        <v>-2.3955</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3439</v>
+        <v>0.3441</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3891</v>
+        <v>-1.4071</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9088</v>
+        <v>-1.9208</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6653</v>
+        <v>-0.6442</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1434</v>
+        <v>0.2834</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0907</v>
+        <v>0.0439</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0526</v>
+        <v>0.2396</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.061</v>
+        <v>-0.3179</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8811</v>
+        <v>0.5185</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9421</v>
+        <v>-0.8364</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0704</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6595</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J10" t="n">
-        <v>1.368</v>
+        <v>1.3617</v>
       </c>
       <c r="K10" t="n">
-        <v>1.368</v>
+        <v>1.3617</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2976</v>
+        <v>-1.2907</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7098</v>
+        <v>0.4517</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6472</v>
+        <v>0.2949</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0914</v>
+        <v>-1.6091</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1862</v>
+        <v>-1.8671</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.258</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9505</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1834</v>
+        <v>-0.1756</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1275</v>
+        <v>1.1261</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3853</v>
+        <v>1.3642</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4951</v>
+        <v>0.4859</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4411</v>
+        <v>-0.4138</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.5786</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3297</v>
+        <v>0.0253</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4282</v>
+        <v>0.5532</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5044</v>
+        <v>-2.9322</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0164</v>
+        <v>-4.7294</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5121</v>
+        <v>1.7973</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5687</v>
+        <v>-2.5884</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.844</v>
+        <v>-0.8525</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7544</v>
+        <v>-1.8023</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3228</v>
+        <v>-0.349</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4316</v>
+        <v>-1.4533</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8143</v>
+        <v>-0.7861</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3061</v>
+        <v>0.913</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0212</v>
+        <v>0.3782</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2849</v>
+        <v>0.5347</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>27.3155</v>
+        <v>27.6806</v>
       </c>
       <c r="E13" t="n">
-        <v>18.3666</v>
+        <v>18.4358</v>
       </c>
       <c r="F13" t="n">
-        <v>8.948899999999998</v>
+        <v>9.244899999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>14.62</v>
+        <v>14.6264</v>
       </c>
       <c r="H13" t="n">
-        <v>4.011399999999998</v>
+        <v>4.0205</v>
       </c>
       <c r="I13" t="n">
-        <v>10.6087</v>
+        <v>10.606</v>
       </c>
       <c r="J13" t="n">
-        <v>19.8341</v>
+        <v>19.6275</v>
       </c>
       <c r="K13" t="n">
-        <v>9.532600000000002</v>
+        <v>9.412500000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3016</v>
+        <v>10.2149</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.2141</v>
+        <v>-5.0012</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.5214</v>
+        <v>-5.392200000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3072</v>
+        <v>0.3909</v>
       </c>
       <c r="P13" t="n">
-        <v>1.134299999999999</v>
+        <v>1.138399999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.476</v>
+        <v>-12.5199</v>
       </c>
       <c r="R13" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>7.5761</v>
+        <v>7.9452</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2986</v>
+        <v>2.6686</v>
       </c>
       <c r="U13" t="n">
-        <v>5.2775</v>
+        <v>5.2764</v>
       </c>
       <c r="V13" t="n">
-        <v>3.985</v>
+        <v>3.970800000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.709499999999998</v>
+        <v>8.6592</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.724600000000001</v>
+        <v>-4.6883</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3771</v>
+        <v>1.4971</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5853</v>
+        <v>1.5349</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2082</v>
+        <v>-0.0378</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.337</v>
+        <v>0.4427</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3693</v>
+        <v>-0.8414</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7063</v>
+        <v>1.284</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2977</v>
+        <v>1.3158</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5514</v>
+        <v>-0.3522</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7463</v>
+        <v>1.668</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6347</v>
+        <v>-0.8731</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1821</v>
+        <v>-0.4891</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4526</v>
+        <v>-0.384</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4201</v>
+        <v>-0.6284</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.378</v>
+        <v>-0.098</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0421</v>
+        <v>-0.5304</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8924</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1853</v>
+        <v>1.3636</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8867</v>
+        <v>4.7208</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.7013</v>
+        <v>-3.3572</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9339</v>
+        <v>1.918</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5123</v>
+        <v>2.5021</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5785</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8491</v>
+        <v>3.8096</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8199</v>
+        <v>3.7954</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9152</v>
+        <v>-1.8916</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8166</v>
+        <v>-0.6227</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3085</v>
+        <v>-0.4255</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5081</v>
+        <v>-0.1972</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1558</v>
+        <v>1.1226</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5632</v>
+        <v>4.3222</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4074</v>
+        <v>-3.1996</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4465</v>
+        <v>-0.3267</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8383</v>
+        <v>0.3732</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2848</v>
+        <v>-0.6998</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3435</v>
+        <v>2.2821</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.333</v>
+        <v>1.5373</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6765</v>
+        <v>0.7447</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8971</v>
+        <v>-2.6087</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5053</v>
+        <v>-1.1642</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3918</v>
+        <v>-1.4446</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9711</v>
+        <v>-0.6889</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0998</v>
+        <v>-0.6137</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8713</v>
+        <v>-0.0752</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>2.8814</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1306</v>
+        <v>-0.3584</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3186</v>
+        <v>0.4129</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4492</v>
+        <v>-0.7712</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8408</v>
+        <v>0.8364</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0548</v>
+        <v>-0.0573</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8956</v>
+        <v>0.8937</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2875</v>
+        <v>2.269</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6856</v>
+        <v>0.6755</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4467</v>
+        <v>-1.4326</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4231</v>
+        <v>-0.6516</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6079</v>
+        <v>-0.4904</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1848</v>
+        <v>-0.1612</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4082</v>
+        <v>-1.2284</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2596</v>
+        <v>-0.1528</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1486</v>
+        <v>-1.0756</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3466</v>
+        <v>0.3511</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3679</v>
+        <v>0.3704</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7456</v>
+        <v>1.7404</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.399</v>
+        <v>-1.3893</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8474</v>
+        <v>-0.669</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4301</v>
+        <v>-0.3692</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.214</v>
+        <v>-2.5684</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4387</v>
+        <v>-0.7042</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2247</v>
+        <v>-1.8642</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3764</v>
+        <v>-2.0467</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3043</v>
+        <v>0.0373</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07199999999999999</v>
+        <v>-2.084</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0844</v>
+        <v>1.0057</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9351</v>
+        <v>1.4307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1493</v>
+        <v>-0.4249</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.708</v>
+        <v>-3.0524</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6308</v>
+        <v>-1.3934</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0772</v>
+        <v>-1.659</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8147</v>
+        <v>-0.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1809</v>
+        <v>-0.7493</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3266</v>
+        <v>-0.7994</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5075</v>
+        <v>0.0501</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8639</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.3817</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2235</v>
+        <v>-2.5687</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2126</v>
+        <v>-2.5755</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0109</v>
+        <v>0.0068</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0484</v>
+        <v>0.3934</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0361</v>
+        <v>0.3126</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0844</v>
+        <v>0.0808</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0214</v>
+        <v>1.0797</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4373</v>
+        <v>0.9308</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4159</v>
+        <v>0.1489</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0698</v>
+        <v>-0.6863</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4012</v>
+        <v>-0.6182</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6685</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4019</v>
+        <v>-0.1881</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3266</v>
+        <v>-0.4441</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.2559</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.8634</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-1.3901</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8515</v>
+        <v>-2.6749</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4016</v>
+        <v>-1.301</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4499</v>
+        <v>-1.3739</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8816</v>
+        <v>-2.884</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3303</v>
+        <v>-1.338</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5513</v>
+        <v>-1.546</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4644</v>
+        <v>-0.4761</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4644</v>
+        <v>-0.4761</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4171</v>
+        <v>-2.4078</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8658</v>
+        <v>-0.8618</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5513</v>
+        <v>-1.546</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2894</v>
+        <v>-0.1081</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1279</v>
+        <v>0.1917</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3302</v>
+        <v>-4.2078</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0758</v>
+        <v>-3.0986</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2544</v>
+        <v>-1.1092</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0875</v>
+        <v>-1.0868</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4531</v>
+        <v>-0.4538</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6344</v>
+        <v>-0.633</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0408</v>
+        <v>-0.0542</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6238</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0467</v>
+        <v>-1.0326</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3108</v>
+        <v>-1.1893</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8347</v>
+        <v>-0.8364</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4761</v>
+        <v>-0.3529</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9085</v>
+        <v>-4.8772</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5224</v>
+        <v>-5.5578</v>
       </c>
       <c r="F23" t="n">
-        <v>0.614</v>
+        <v>0.6806</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.3428</v>
+        <v>-4.3527</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4156</v>
+        <v>-2.4127</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9273</v>
+        <v>-1.94</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.9921</v>
+        <v>-4.0244</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9262</v>
+        <v>-1.938</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.066</v>
+        <v>-2.0864</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3507</v>
+        <v>-0.3284</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3103</v>
+        <v>-0.2788</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1693</v>
+        <v>-0.1677</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.141</v>
+        <v>-0.1111</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1654</v>
+        <v>-5.8331</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4168</v>
+        <v>-4.3153</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7486</v>
+        <v>-1.5177</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.3592</v>
+        <v>-4.3603</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1788</v>
+        <v>-2.1826</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1804</v>
+        <v>-2.1777</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2725</v>
+        <v>-2.2827</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4861</v>
+        <v>-1.4931</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0867</v>
+        <v>-2.0775</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.672</v>
+        <v>-0.3346</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5565</v>
+        <v>-0.4392</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1155</v>
+        <v>0.1046</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8019</v>
+        <v>-6.2089</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0678</v>
+        <v>-3.6198</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7342</v>
+        <v>-2.5891</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.5078</v>
+        <v>-3.5108</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3304</v>
+        <v>-0.3303</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.1773</v>
+        <v>-3.1805</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6452</v>
+        <v>-1.6637</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.7247</v>
+        <v>-1.7359</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8626</v>
+        <v>-1.8471</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2942</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4594</v>
+        <v>-0.3355</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-27.3156</v>
+        <v>-26.5425</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.0415</v>
+        <v>-10.3342</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.274</v>
+        <v>-16.2081</v>
       </c>
       <c r="G26" t="n">
-        <v>-14.6201</v>
+        <v>-14.6264</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.0114</v>
+        <v>-4.0205</v>
       </c>
       <c r="I26" t="n">
-        <v>-10.6088</v>
+        <v>-10.606</v>
       </c>
       <c r="J26" t="n">
-        <v>5.214199999999998</v>
+        <v>5.001200000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>5.521500000000001</v>
+        <v>5.3924</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.3073999999999995</v>
+        <v>-0.3910999999999993</v>
       </c>
       <c r="M26" t="n">
-        <v>-19.8343</v>
+        <v>-19.6274</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.5327</v>
+        <v>-9.412599999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-10.3014</v>
+        <v>-10.215</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6099</v>
+        <v>-13.6579</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.576</v>
+        <v>-6.806900000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.277399999999999</v>
+        <v>-5.2767</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.2987</v>
+        <v>-1.5304</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.9852</v>
+        <v>-3.971</v>
       </c>
       <c r="W26" t="n">
-        <v>3.6318</v>
+        <v>3.5988</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.616999999999998</v>
+        <v>-7.5697</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104507_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104507_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.6883</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104507_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.5697</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
